--- a/analysis/tables/pythia-70m.xlsx
+++ b/analysis/tables/pythia-70m.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4183426295418958</v>
+        <v>0.3039956441337776</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0961588978903285</v>
+        <v>-0.05153568407252632</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.418x - 0.096</t>
+          <t>y = 0.304x - 0.052</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.4301879219231377</v>
+        <v>0.4301879219231376</v>
       </c>
       <c r="H3" t="n">
         <v>0.07050635003272662</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2298567994268881</v>
+        <v>0.1695277056333324</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3221837316515673</v>
+        <v>0.2524599600612513</v>
       </c>
       <c r="K3" t="n">
         <v>0.0545787772368142</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.2989409674786</v>
+        <v>0.3035408006889746</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0604309775973228</v>
+        <v>-0.04840770965799931</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 10.299x + 0.060</t>
+          <t>y = 0.304x - 0.048</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5848256037548677</v>
+        <v>0.4338813760968098</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06783051568692694</v>
+        <v>0.07044243888626163</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005867688511677873</v>
+        <v>0.159476780545231</v>
       </c>
       <c r="J4" t="n">
-        <v>10.35937194507593</v>
+        <v>0.2551330910309753</v>
       </c>
       <c r="K4" t="n">
         <v>0.0545787772368142</v>
